--- a/data/trans_dic/P6907S1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 18,1</t>
+          <t>3,81; 17,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 22,47</t>
+          <t>2,4; 20,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,42</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 26,97</t>
+          <t>6,3; 27,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,9</t>
+          <t>0,0; 20,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,91</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,2</t>
+          <t>0,84; 7,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,14</t>
+          <t>3,56; 14,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,53</t>
+          <t>1,6; 14,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 17,43</t>
+          <t>4,14; 17,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 18,45</t>
+          <t>6,38; 18,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,52</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,76</t>
+          <t>1,03; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 20,56</t>
+          <t>7,06; 20,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 22,88</t>
+          <t>4,07; 23,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,48</t>
+          <t>1,66; 15,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,45</t>
+          <t>2,71; 10,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 17,05</t>
+          <t>7,6; 18,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,4</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,86</t>
+          <t>1,37; 8,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,12</t>
+          <t>5,68; 13,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 15,31</t>
+          <t>3,47; 15,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,35</t>
+          <t>0,0; 13,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,37</t>
+          <t>0,85; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,91</t>
+          <t>2,73; 20,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,73</t>
+          <t>2,12; 18,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,37</t>
+          <t>0,0; 20,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 24,19</t>
+          <t>3,55; 23,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 13,58</t>
+          <t>4,1; 13,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,63</t>
+          <t>1,25; 10,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,9</t>
+          <t>0,53; 5,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,94</t>
+          <t>4,83; 18,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,58</t>
+          <t>4,32; 12,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,43</t>
+          <t>0,0; 12,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,41</t>
+          <t>2,01; 11,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,42</t>
+          <t>3,62; 14,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,2</t>
+          <t>7,2; 21,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,0</t>
+          <t>0,0; 21,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 8,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 16,34</t>
+          <t>5,18; 15,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,41</t>
+          <t>6,56; 14,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,44</t>
+          <t>1,51; 11,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,77</t>
+          <t>1,36; 7,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,01</t>
+          <t>5,6; 12,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,13</t>
+          <t>6,84; 12,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,72</t>
+          <t>2,6; 10,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,03</t>
+          <t>1,76; 5,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,11</t>
+          <t>7,76; 15,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,58</t>
+          <t>7,24; 16,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,73</t>
+          <t>0,86; 7,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,44</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,59</t>
+          <t>5,48; 11,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,22</t>
+          <t>7,53; 12,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,57</t>
+          <t>2,25; 7,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,76</t>
+          <t>1,85; 5,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,05</t>
+          <t>7,24; 12,19</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3112; 14355</t>
+          <t>3020; 14095</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>840; 7724</t>
+          <t>826; 7168</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6246</t>
+          <t>0; 6252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4412; 19210</t>
+          <t>4484; 19572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5772</t>
+          <t>0; 6620</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4161</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>466; 3939</t>
+          <t>459; 4099</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4228; 15773</t>
+          <t>3975; 16200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>838; 7581</t>
+          <t>833; 7677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7597</t>
+          <t>0; 7661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5256; 21941</t>
+          <t>5210; 21565</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9620; 26940</t>
+          <t>9317; 26951</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6300</t>
+          <t>0; 6280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>989; 8491</t>
+          <t>996; 8314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8239; 23027</t>
+          <t>7908; 22938</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2811; 12080</t>
+          <t>2150; 12502</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1965</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>941; 9153</t>
+          <t>924; 8468</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2563; 10317</t>
+          <t>2673; 10358</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14413; 33887</t>
+          <t>15110; 36397</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6118</t>
+          <t>0; 6276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2863; 13514</t>
+          <t>2096; 13284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12920; 29746</t>
+          <t>11966; 28909</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3036; 16832</t>
+          <t>3812; 17274</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6016</t>
+          <t>0; 5841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>921; 8100</t>
+          <t>935; 8661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1110; 10450</t>
+          <t>1510; 11394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>976; 9182</t>
+          <t>986; 8838</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 6393</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3736; 23437</t>
+          <t>3441; 23122</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6453; 21242</t>
+          <t>6414; 21437</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>916; 7777</t>
+          <t>913; 7834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929; 8552</t>
+          <t>930; 8854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7539; 28827</t>
+          <t>7356; 27951</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6276; 17240</t>
+          <t>5924; 17775</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 4091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1789; 10090</t>
+          <t>1778; 10074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3752; 15580</t>
+          <t>3658; 14916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6141; 18771</t>
+          <t>6375; 18997</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5790</t>
+          <t>0; 5677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 5497</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5310; 16981</t>
+          <t>5381; 16511</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15109; 32509</t>
+          <t>14806; 32221</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>862; 7285</t>
+          <t>886; 6756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2012; 12011</t>
+          <t>2103; 11993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11419; 26655</t>
+          <t>11474; 26206</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31374; 57283</t>
+          <t>32292; 57892</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3828; 13864</t>
+          <t>3708; 15108</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6822; 21090</t>
+          <t>6155; 20359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26759; 51294</t>
+          <t>26360; 51777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16145; 34298</t>
+          <t>15931; 35361</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>901; 7739</t>
+          <t>865; 7292</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1873; 11770</t>
+          <t>1914; 12838</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19193; 41055</t>
+          <t>19415; 41707</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52223; 84638</t>
+          <t>52127; 84594</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5690; 18377</t>
+          <t>5467; 18786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10744; 26956</t>
+          <t>10465; 29009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49477; 83611</t>
+          <t>50220; 84552</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6907S1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 17,77</t>
+          <t>3,81; 17,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 20,85</t>
+          <t>2,45; 22,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 27,48</t>
+          <t>5,75; 28,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,53</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 14,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,5</t>
+          <t>0,81; 7,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,52</t>
+          <t>4,09; 14,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,71</t>
+          <t>1,61; 15,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 17,13</t>
+          <t>4,03; 17,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 18,46</t>
+          <t>6,58; 19,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 19,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,57</t>
+          <t>1,04; 9,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 20,48</t>
+          <t>6,68; 17,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 23,68</t>
+          <t>4,07; 21,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,24</t>
+          <t>1,69; 16,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,49</t>
+          <t>2,58; 10,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,31</t>
+          <t>7,54; 17,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,67</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,71</t>
+          <t>1,96; 9,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,72</t>
+          <t>5,29; 12,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 15,71</t>
+          <t>3,33; 15,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,93</t>
+          <t>0,0; 15,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,88</t>
+          <t>0,84; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 20,61</t>
+          <t>3,53; 22,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 18,99</t>
+          <t>2,13; 19,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,47</t>
+          <t>0,0; 14,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 23,86</t>
+          <t>10,95; 28,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 13,7</t>
+          <t>4,14; 13,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,71</t>
+          <t>1,26; 10,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,07</t>
+          <t>0,53; 4,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 18,37</t>
+          <t>9,35; 23,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,97</t>
+          <t>4,39; 13,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,68</t>
+          <t>0,0; 14,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,39</t>
+          <t>2,02; 12,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,76</t>
+          <t>3,25; 13,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 21,45</t>
+          <t>7,23; 21,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,57</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,32</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 15,89</t>
+          <t>6,29; 17,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,28</t>
+          <t>6,36; 14,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,53</t>
+          <t>1,52; 12,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,76</t>
+          <t>1,73; 7,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 12,79</t>
+          <t>6,0; 13,35</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,26</t>
+          <t>6,61; 12,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,6</t>
+          <t>2,62; 10,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,82</t>
+          <t>1,74; 5,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,25</t>
+          <t>7,27; 14,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,06</t>
+          <t>7,03; 15,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,28</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,77</t>
+          <t>6,68; 12,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,22</t>
+          <t>7,72; 12,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,74</t>
+          <t>2,42; 7,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,12</t>
+          <t>1,91; 4,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,19</t>
+          <t>7,54; 12,29</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11433</t>
         </is>
       </c>
     </row>
@@ -1645,27 +1645,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3020; 14095</t>
+          <t>3019; 13751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>826; 7168</t>
+          <t>842; 7725</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6252</t>
+          <t>0; 6215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4484; 19572</t>
+          <t>4318; 21181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6620</t>
+          <t>0; 5819</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4332</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>459; 4099</t>
+          <t>483; 4394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3975; 16200</t>
+          <t>4566; 16541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>833; 7677</t>
+          <t>842; 8110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7661</t>
+          <t>0; 7543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5210; 21565</t>
+          <t>5436; 23949</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>20099</t>
         </is>
       </c>
     </row>
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9317; 26951</t>
+          <t>9607; 28062</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6280</t>
+          <t>0; 6746</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>996; 8314</t>
+          <t>1004; 9023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7908; 22938</t>
+          <t>8884; 23575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2150; 12502</t>
+          <t>2147; 11576</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1883,32 +1883,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>924; 8468</t>
+          <t>940; 9098</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2673; 10358</t>
+          <t>2771; 11043</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15110; 36397</t>
+          <t>14990; 35486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6276</t>
+          <t>0; 6299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2096; 13284</t>
+          <t>2984; 14006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11966; 28909</t>
+          <t>12731; 30545</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>20183</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3812; 17274</t>
+          <t>3664; 16629</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5841</t>
+          <t>0; 6457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>935; 8661</t>
+          <t>925; 8254</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1510; 11394</t>
+          <t>2428; 15187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>986; 8838</t>
+          <t>993; 9137</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6393</t>
+          <t>0; 4500</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3441; 23122</t>
+          <t>7742; 20142</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6414; 21437</t>
+          <t>6480; 20637</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>913; 7834</t>
+          <t>923; 7939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930; 8854</t>
+          <t>931; 8359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7356; 27951</t>
+          <t>13047; 32311</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>19635</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5924; 17775</t>
+          <t>6021; 17938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4091</t>
+          <t>0; 4666</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1778; 10074</t>
+          <t>1789; 10696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3658; 14916</t>
+          <t>3511; 14830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6375; 18997</t>
+          <t>6405; 19240</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 5700</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5497</t>
+          <t>0; 5610</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5381; 16511</t>
+          <t>6750; 18396</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14806; 32221</t>
+          <t>14342; 31613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>886; 6756</t>
+          <t>892; 7571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2103; 11993</t>
+          <t>2675; 12306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11474; 26206</t>
+          <t>12933; 28773</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>71351</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32292; 57892</t>
+          <t>31212; 58423</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3708; 15108</t>
+          <t>3736; 14741</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6155; 20359</t>
+          <t>6088; 20082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26360; 51777</t>
+          <t>27991; 56998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15931; 35361</t>
+          <t>15468; 33934</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>865; 7292</t>
+          <t>881; 7526</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1914; 12838</t>
+          <t>1754; 11305</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19415; 41707</t>
+          <t>23061; 43184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52127; 84594</t>
+          <t>53477; 84837</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5467; 18786</t>
+          <t>5871; 19125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10465; 29009</t>
+          <t>10833; 28057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50220; 84552</t>
+          <t>55032; 89745</t>
         </is>
       </c>
     </row>
